--- a/artfynd/A 2173-2026 artfynd.xlsx
+++ b/artfynd/A 2173-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>78930434</v>
+        <v>137370568</v>
       </c>
       <c r="B2" t="n">
-        <v>80432</v>
+        <v>97647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hjältestorpet, biotopskydd intill Ygeltjärnsbäcken, Jmt</t>
+          <t>Klippen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583939</v>
+        <v>583795</v>
       </c>
       <c r="R2" t="n">
-        <v>6978936</v>
+        <v>6978826</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-06-28</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-06-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,83 +775,72 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Barrnaturskog med lövinslag</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Asp 40 cm</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
+          <t>Marie Israelsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Karelsk barkfluga i sydöstra Jämtland</t>
-        </is>
-      </c>
+          <t>Marie Israelsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78930434</t>
+          <t>https://artportalen.se/Sighting/137370568</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>78930395</v>
+        <v>137370566</v>
       </c>
       <c r="B3" t="n">
-        <v>80461</v>
+        <v>80632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hjältestorpet, biotopskydd intill Ygeltjärnsbäcken, Jmt</t>
+          <t>Klippen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583939</v>
+        <v>583904</v>
       </c>
       <c r="R3" t="n">
-        <v>6978936</v>
+        <v>6978822</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,17 +864,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-06-28</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-06-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Lite</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,67 +890,53 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Barrnaturskog med lövinslag</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Asp 40 cm</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
+          <t>Marie Israelsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Karelsk barkfluga i sydöstra Jämtland</t>
-        </is>
-      </c>
+          <t>Marie Israelsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78930395</t>
+          <t>https://artportalen.se/Sighting/137370566</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>78930451</v>
+        <v>78930434</v>
       </c>
       <c r="B4" t="n">
-        <v>80392</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1037,7 +1026,595 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/78930434</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137370569</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80631</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Klippen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>583927</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6978862</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Marie Israelsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Marie Israelsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137370569</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>78930395</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hjältestorpet, biotopskydd intill Ygeltjärnsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>583939</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6978936</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2019-06-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2019-06-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Lite</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Barrnaturskog med lövinslag</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Asp 40 cm</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Karelsk barkfluga i sydöstra Jämtland</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78930395</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137370567</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80642</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Klippen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>583927</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6978862</v>
+      </c>
+      <c r="S7" t="n">
+        <v>7</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Marie Israelsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Marie Israelsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137370567</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>78930451</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hjältestorpet, biotopskydd intill Ygeltjärnsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>583939</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6978936</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-06-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-06-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Barrnaturskog med lövinslag</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Asp 40 cm</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Karelsk barkfluga i sydöstra Jämtland</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/78930451</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137370563</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80581</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Klippen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>583924</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6978868</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Marie Israelsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Marie Israelsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137370563</t>
         </is>
       </c>
     </row>
@@ -1046,6 +1623,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2173-2026 artfynd.xlsx
+++ b/artfynd/A 2173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370568</v>
       </c>
       <c r="B2" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2173-2026 artfynd.xlsx
+++ b/artfynd/A 2173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370568</v>
       </c>
       <c r="B2" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137370566</v>
       </c>
       <c r="B3" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>137370569</v>
       </c>
       <c r="B5" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>137370567</v>
       </c>
       <c r="B7" t="n">
-        <v>80642</v>
+        <v>80647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>137370563</v>
       </c>
       <c r="B9" t="n">
-        <v>80581</v>
+        <v>80586</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 2173-2026 artfynd.xlsx
+++ b/artfynd/A 2173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370568</v>
       </c>
       <c r="B2" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137370566</v>
       </c>
       <c r="B3" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>137370569</v>
       </c>
       <c r="B5" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>137370567</v>
       </c>
       <c r="B7" t="n">
-        <v>80647</v>
+        <v>80658</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>137370563</v>
       </c>
       <c r="B9" t="n">
-        <v>80586</v>
+        <v>80597</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 2173-2026 artfynd.xlsx
+++ b/artfynd/A 2173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370568</v>
       </c>
       <c r="B2" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137370566</v>
       </c>
       <c r="B3" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>137370569</v>
       </c>
       <c r="B5" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>137370567</v>
       </c>
       <c r="B7" t="n">
-        <v>80658</v>
+        <v>80659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>137370563</v>
       </c>
       <c r="B9" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 2173-2026 artfynd.xlsx
+++ b/artfynd/A 2173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370568</v>
       </c>
       <c r="B2" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137370566</v>
       </c>
       <c r="B3" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>137370569</v>
       </c>
       <c r="B5" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>137370567</v>
       </c>
       <c r="B7" t="n">
-        <v>80659</v>
+        <v>80661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>137370563</v>
       </c>
       <c r="B9" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 2173-2026 artfynd.xlsx
+++ b/artfynd/A 2173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370568</v>
       </c>
       <c r="B2" t="n">
-        <v>97671</v>
+        <v>97675</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>137370566</v>
       </c>
       <c r="B3" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>137370569</v>
       </c>
       <c r="B5" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>137370567</v>
       </c>
       <c r="B7" t="n">
-        <v>80661</v>
+        <v>80665</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>137370563</v>
       </c>
       <c r="B9" t="n">
-        <v>80600</v>
+        <v>80604</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
